--- a/data/trans_bre/P19C08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C08-Habitat-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,88</t>
+          <t>-0,6; 0,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,31</t>
+          <t>-0,18; 1,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,01</t>
+          <t>-1,59; -0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,83; 293,19</t>
+          <t>-74,64; 301,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,73</t>
+          <t>-0,13; 0,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,69</t>
+          <t>-0,92; 0,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,28</t>
+          <t>-0,42; 0,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 0,52</t>
+          <t>-0,04; 0,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,75</t>
+          <t>-0,9; 0,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -0,32</t>
+          <t>-2,2; -0,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,17</t>
+          <t>-0,3; 1,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,38</t>
+          <t>-2,61; 0,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-95,32; 93,59</t>
+          <t>-93,73; 86,48</t>
         </is>
       </c>
     </row>
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,36</t>
+          <t>-0,39; 1,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,25</t>
+          <t>-0,25; 1,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,0</t>
+          <t>-0,67; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,8</t>
+          <t>-0,31; 0,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,24; 846,26</t>
+          <t>-61,69; 726,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 918,04</t>
+          <t>-54,91; 993,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,57; 693,41</t>
+          <t>-66,07; 686,43</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,58</t>
+          <t>-0,16; 0,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,39</t>
+          <t>-0,46; 0,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,29</t>
+          <t>-0,15; 0,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,23</t>
+          <t>-0,5; 0,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 294,33</t>
+          <t>-37,19; 318,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-52,14; 98,65</t>
+          <t>-53,59; 89,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-84,06; 583,59</t>
+          <t>-83,28; 704,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-64,0; 93,55</t>
+          <t>-66,69; 84,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C08-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-78,26%</t>
+          <t>-76,91%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,75</t>
+          <t>-0,44; 0,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,35</t>
+          <t>-0,94; 1,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,1</t>
+          <t>-0,18; 1,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; -0,0</t>
+          <t>-1,5; 0,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,64; 301,5</t>
+          <t>-74,88; 301,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>325,04%</t>
+          <t>236,35%</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,87</t>
+          <t>-0,24; 0,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,63</t>
+          <t>-0,98; 0,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 0,42</t>
+          <t>-0,06; 0,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,51</t>
+          <t>-0,4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-50,0%</t>
+          <t>-31,97%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,82</t>
+          <t>-0,89; 0,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; -0,32</t>
+          <t>-2,62; -0,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,25</t>
+          <t>-0,3; 1,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,25</t>
+          <t>-1,96; 0,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-93,73; 86,48</t>
+          <t>-83,96; 129,41</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,64%</t>
         </is>
       </c>
     </row>
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,37</t>
+          <t>-0,38; 1,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,16</t>
+          <t>-0,16; 1,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,0</t>
+          <t>-0,81; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,84</t>
+          <t>-0,3; 0,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,69; 726,53</t>
+          <t>-64,1; 678,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,91; 993,61</t>
+          <t>-41,73; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 686,43</t>
+          <t>-68,7; 666,39</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-15,38%</t>
+          <t>-16,26%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,57</t>
+          <t>-0,13; 0,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,37</t>
+          <t>-0,45; 0,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,3</t>
+          <t>-0,17; 0,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,23</t>
+          <t>-0,49; 0,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 318,01</t>
+          <t>-35,19; 304,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-53,59; 89,82</t>
+          <t>-52,5; 103,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-83,28; 704,03</t>
+          <t>-72,0; 772,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-66,69; 84,01</t>
+          <t>-60,89; 70,59</t>
         </is>
       </c>
     </row>
